--- a/data/data/ICICI Prudential Mutual Fund/ICICI Prudential Silver ETF Fund of Fund.xlsx
+++ b/data/data/ICICI Prudential Mutual Fund/ICICI Prudential Silver ETF Fund of Fund.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\mumchfnp01\RatingFinance\Factseet Mandates\ICICI PRUDENTIAL FACTSHEET\2025\Feb\Portfolio stage 8\Riskometer updated Portfolio\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\mumchfnp01\RatingFinance\Factseet Mandates\ICICI PRUDENTIAL FACTSHEET\2025\June\Portfolio stage 8\Riskometer updated portfolio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B23A11BD-45CE-4820-B227-7504A9D52292}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69C1EBB3-6E64-4C27-A08F-C00CBF3F1899}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
     <t>ICICI Prudential Silver ETF Fund of Fund</t>
   </si>
   <si>
-    <t>Portfolio as on Jan 31,2025</t>
+    <t>Portfolio as on May 31,2025</t>
   </si>
   <si>
     <t>Company/Issuer/Instrument Name</t>
@@ -61,7 +61,7 @@
     <t/>
   </si>
   <si>
-    <t>ICICI PRUDENTIAL SILVER ETF</t>
+    <t>ICICI PRUDENTIAL SILVER ETF null</t>
   </si>
   <si>
     <t>INF109KC1Y56</t>
@@ -85,7 +85,7 @@
     <t>@ As per AMFI Best Practices Guidelines Circular No. 91/ 2020 - 21 dated March 24, 2021 on Valuation of AT-1 Bonds and Tier 2 Bonds, Yield to call is disclosed for AT-1 Bonds and Tier 2 Bonds issued by Banks as provided by Valuation agencies.</t>
   </si>
   <si>
-    <t>For Instances of Deviation In valuation Of Securities as per SEBI master circular ref no SEBI/HO/IMD/IMD-PoD-1/P/CIR/2023/74 dated May 19, 2023.Refer link: https://www.icicipruamc.com/statutory-disclosures/deviation-in-valuation-of-securities</t>
+    <t>For Instances of Deviation In valuation Of Securities as per SEBI master circular ref no SEBI/HO/IMD/IMD-PoD-1/P/CIR/2024/90 dated June 27, 2024. Refer link: https://www.icicipruamc.com/about-us/statutory-disclosures?currentTabFilter=OtherDisclosures&amp;&amp;subCatTabFilter=deviationinvaluationofsecurities</t>
   </si>
   <si>
     <t>As per AMFI Best Practices Guidelines Circular No. AMFI/ 35P/ MEM-COR/ 72 / 2022-23 dated December 31, 2022 on Standard format for disclosure Portfolio YTM for Debt Schemes, Yield of the instrument is disclosed on annualized basis as provided by Valuation agencies.</t>
@@ -121,13 +121,13 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="8.25"/>
-      <name val="Microsoft Sans Serif"/>
+      <sz val="8.5"/>
+      <name val="Verdana"/>
       <family val="2"/>
     </font>
     <font>
-      <sz val="8.5"/>
-      <name val="Verdana"/>
+      <sz val="8.25"/>
+      <name val="Microsoft Sans Serif"/>
       <family val="2"/>
     </font>
     <font>
@@ -257,14 +257,7 @@
   </cellStyleXfs>
   <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="top"/>
       <protection locked="0"/>
@@ -277,6 +270,13 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -292,20 +292,20 @@
     <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -313,7 +313,7 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="top"/>
       <protection locked="0"/>
     </xf>
@@ -375,7 +375,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="666750" y="4648200"/>
+          <a:off x="666750" y="4591050"/>
           <a:ext cx="2771775" cy="1905000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -422,7 +422,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="666750" y="7505700"/>
+          <a:off x="666750" y="7448550"/>
           <a:ext cx="2771775" cy="1905000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -759,12 +759,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J36"/>
-  <sheetFormatPr defaultColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="10" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10" style="23" customWidth="1" collapsed="1"/>
     <col min="2" max="2" width="41.5703125" style="23" bestFit="1" customWidth="1" collapsed="1"/>
     <col min="3" max="3" width="16.140625" style="23" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="19.5703125" style="23" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="19.7109375" style="23" bestFit="1" customWidth="1" collapsed="1"/>
     <col min="5" max="5" width="12.28515625" style="23" bestFit="1" customWidth="1" collapsed="1"/>
     <col min="6" max="6" width="38.7109375" style="23" bestFit="1" customWidth="1" collapsed="1"/>
     <col min="7" max="7" width="11.7109375" style="23" bestFit="1" customWidth="1" collapsed="1"/>
@@ -774,45 +774,45 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="4"/>
+      <c r="H1" s="4"/>
+      <c r="I1" s="4"/>
+      <c r="J1" s="4"/>
     </row>
     <row r="2" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5"/>
-      <c r="H2" s="5"/>
-      <c r="I2" s="5"/>
-      <c r="J2" s="5"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
     </row>
     <row r="3" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4"/>
-      <c r="G3" s="4"/>
-      <c r="H3" s="4"/>
-      <c r="I3" s="4"/>
-      <c r="J3" s="4"/>
-    </row>
-    <row r="4" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2"/>
+    </row>
+    <row r="4" spans="2:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B4" s="7" t="s">
         <v>3</v>
       </c>
@@ -852,10 +852,10 @@
         <v>12</v>
       </c>
       <c r="F5" s="12">
-        <v>100510.19</v>
+        <v>125177.66</v>
       </c>
       <c r="G5" s="13">
-        <v>0.99664672362569995</v>
+        <v>0.99684514685079995</v>
       </c>
       <c r="H5" s="12" t="s">
         <v>12</v>
@@ -875,13 +875,13 @@
         <v>15</v>
       </c>
       <c r="E6" s="17">
-        <v>106574264</v>
+        <v>127290690</v>
       </c>
       <c r="F6" s="18">
-        <v>100510.19</v>
+        <v>125177.66</v>
       </c>
       <c r="G6" s="19">
-        <v>0.99664672362569995</v>
+        <v>0.99684514685079995</v>
       </c>
       <c r="H6" s="18" t="s">
         <v>12</v>
@@ -912,10 +912,10 @@
         <v>12</v>
       </c>
       <c r="F8" s="12">
-        <v>498.12</v>
+        <v>1049.82</v>
       </c>
       <c r="G8" s="13">
-        <v>4.9392968609999997E-3</v>
+        <v>8.3601816176000002E-3</v>
       </c>
       <c r="H8" s="12" t="s">
         <v>12</v>
@@ -946,10 +946,10 @@
         <v>12</v>
       </c>
       <c r="F10" s="21">
-        <v>-159.9475688800012</v>
+        <v>-653.65301649000321</v>
       </c>
       <c r="G10" s="22">
-        <v>-1.5860204868397966E-3</v>
+        <v>-5.2053284684541708E-3</v>
       </c>
       <c r="H10" s="21" t="s">
         <v>12</v>
@@ -972,10 +972,10 @@
         <v>12</v>
       </c>
       <c r="F11" s="21">
-        <v>100848.36243112</v>
+        <v>125573.82698351001</v>
       </c>
       <c r="G11" s="22">
-        <v>0.99999999999986022</v>
+        <v>0.99999999999994582</v>
       </c>
       <c r="H11" s="21" t="s">
         <v>12</v>
@@ -985,60 +985,60 @@
       </c>
     </row>
     <row r="14" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2"/>
+      <c r="C14" s="5"/>
+      <c r="D14" s="5"/>
+      <c r="E14" s="5"/>
+      <c r="F14" s="5"/>
+      <c r="G14" s="5"/>
+      <c r="H14" s="5"/>
     </row>
     <row r="15" spans="2:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="1" t="s">
+      <c r="B15" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
-      <c r="F15" s="2"/>
-      <c r="G15" s="2"/>
-      <c r="H15" s="2"/>
+      <c r="C15" s="5"/>
+      <c r="D15" s="5"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="5"/>
+      <c r="G15" s="5"/>
+      <c r="H15" s="5"/>
     </row>
     <row r="16" spans="2:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B16" s="1" t="s">
+      <c r="B16" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="C16" s="2"/>
-      <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
-      <c r="F16" s="2"/>
-      <c r="G16" s="2"/>
-      <c r="H16" s="2"/>
+      <c r="C16" s="5"/>
+      <c r="D16" s="5"/>
+      <c r="E16" s="5"/>
+      <c r="F16" s="5"/>
+      <c r="G16" s="5"/>
+      <c r="H16" s="5"/>
     </row>
     <row r="17" spans="2:8" ht="27.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B17" s="1" t="s">
+      <c r="B17" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="C17" s="2"/>
-      <c r="D17" s="2"/>
-      <c r="E17" s="2"/>
-      <c r="F17" s="2"/>
-      <c r="G17" s="2"/>
-      <c r="H17" s="2"/>
-    </row>
-    <row r="20" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="C17" s="5"/>
+      <c r="D17" s="5"/>
+      <c r="E17" s="5"/>
+      <c r="F17" s="5"/>
+      <c r="G17" s="5"/>
+      <c r="H17" s="5"/>
+    </row>
+    <row r="20" spans="2:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B20" s="23" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="35" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B35" s="23" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="36" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="36" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B36" s="23" t="s">
         <v>25</v>
       </c>
